--- a/docs/LIRAa Dados.xlsx
+++ b/docs/LIRAa Dados.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:K68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,6 +435,15 @@
       <c r="H1" t="str">
         <v>Alb</v>
       </c>
+      <c r="I1" t="str">
+        <v>Inf.Predial</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Breteau</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Alb</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -453,12 +462,21 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1.4</v>
+      </c>
+      <c r="J2">
+        <v>3.5</v>
+      </c>
+      <c r="K2">
         <v>0</v>
       </c>
     </row>
@@ -479,12 +497,21 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>0</v>
       </c>
     </row>
@@ -508,9 +535,18 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
     </row>
@@ -531,12 +567,21 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>0</v>
       </c>
     </row>
@@ -557,12 +602,21 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>2.1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
     </row>
@@ -583,12 +637,21 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>0</v>
       </c>
     </row>
@@ -609,12 +672,21 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>0</v>
       </c>
     </row>
@@ -643,6 +715,15 @@
       <c r="H9">
         <v>0</v>
       </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -669,6 +750,15 @@
       <c r="H10">
         <v>0</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -687,12 +777,21 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>0</v>
       </c>
     </row>
@@ -721,6 +820,15 @@
       <c r="H12">
         <v>0</v>
       </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -747,6 +855,15 @@
       <c r="H13">
         <v>0</v>
       </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -773,6 +890,15 @@
       <c r="H14">
         <v>0</v>
       </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -799,6 +925,15 @@
       <c r="H15">
         <v>0</v>
       </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -820,10 +955,19 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>2.7</v>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -851,6 +995,15 @@
       <c r="H17">
         <v>0</v>
       </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -877,6 +1030,15 @@
       <c r="H18">
         <v>0</v>
       </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -903,6 +1065,15 @@
       <c r="H19">
         <v>0</v>
       </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -929,6 +1100,15 @@
       <c r="H20">
         <v>0</v>
       </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -955,6 +1135,15 @@
       <c r="H21">
         <v>0</v>
       </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -981,6 +1170,15 @@
       <c r="H22">
         <v>0</v>
       </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -999,12 +1197,21 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>0</v>
       </c>
     </row>
@@ -1033,6 +1240,15 @@
       <c r="H24">
         <v>0</v>
       </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1059,6 +1275,15 @@
       <c r="H25">
         <v>0</v>
       </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1085,6 +1310,15 @@
       <c r="H26">
         <v>0</v>
       </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1111,6 +1345,15 @@
       <c r="H27">
         <v>0</v>
       </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1137,6 +1380,15 @@
       <c r="H28">
         <v>0</v>
       </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1163,6 +1415,15 @@
       <c r="H29">
         <v>0</v>
       </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1189,6 +1450,15 @@
       <c r="H30">
         <v>0</v>
       </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1215,6 +1485,15 @@
       <c r="H31">
         <v>0</v>
       </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1241,6 +1520,15 @@
       <c r="H32">
         <v>0</v>
       </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1267,6 +1555,15 @@
       <c r="H33">
         <v>0</v>
       </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1293,6 +1590,15 @@
       <c r="H34">
         <v>0</v>
       </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1319,6 +1625,15 @@
       <c r="H35">
         <v>0</v>
       </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1345,6 +1660,15 @@
       <c r="H36">
         <v>0</v>
       </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1371,6 +1695,15 @@
       <c r="H37">
         <v>0</v>
       </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1397,6 +1730,15 @@
       <c r="H38">
         <v>0</v>
       </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1423,6 +1765,15 @@
       <c r="H39">
         <v>0</v>
       </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1449,6 +1800,15 @@
       <c r="H40">
         <v>0</v>
       </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1475,6 +1835,15 @@
       <c r="H41">
         <v>0</v>
       </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1501,6 +1870,15 @@
       <c r="H42">
         <v>0</v>
       </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1527,6 +1905,15 @@
       <c r="H43">
         <v>0</v>
       </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1553,6 +1940,15 @@
       <c r="H44">
         <v>0</v>
       </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1579,6 +1975,15 @@
       <c r="H45">
         <v>0</v>
       </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1605,6 +2010,15 @@
       <c r="H46">
         <v>0</v>
       </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1631,6 +2045,15 @@
       <c r="H47">
         <v>0</v>
       </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1657,6 +2080,15 @@
       <c r="H48">
         <v>0</v>
       </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1683,6 +2115,15 @@
       <c r="H49">
         <v>0</v>
       </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1709,6 +2150,15 @@
       <c r="H50">
         <v>0</v>
       </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1735,6 +2185,15 @@
       <c r="H51">
         <v>0</v>
       </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1761,6 +2220,15 @@
       <c r="H52">
         <v>0</v>
       </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1787,6 +2255,15 @@
       <c r="H53">
         <v>0</v>
       </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1813,6 +2290,15 @@
       <c r="H54">
         <v>0</v>
       </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1839,6 +2325,15 @@
       <c r="H55">
         <v>0</v>
       </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1865,6 +2360,15 @@
       <c r="H56">
         <v>0</v>
       </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1891,6 +2395,15 @@
       <c r="H57">
         <v>0</v>
       </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1917,6 +2430,15 @@
       <c r="H58">
         <v>0</v>
       </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1943,6 +2465,15 @@
       <c r="H59">
         <v>0</v>
       </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1969,6 +2500,15 @@
       <c r="H60">
         <v>0</v>
       </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1995,6 +2535,15 @@
       <c r="H61">
         <v>0</v>
       </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2021,6 +2570,15 @@
       <c r="H62">
         <v>0</v>
       </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2047,6 +2605,15 @@
       <c r="H63">
         <v>0</v>
       </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -2073,6 +2640,15 @@
       <c r="H64">
         <v>0</v>
       </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2091,13 +2667,22 @@
         <v>0.0</v>
       </c>
       <c r="F65" t="str">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="str">
         <v>0.0</v>
       </c>
       <c r="H65" t="str">
-        <v>2.7</v>
+        <v>0.0</v>
+      </c>
+      <c r="I65" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="J65" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -2116,15 +2701,26 @@
         <v>C2</v>
       </c>
       <c r="B67" t="str">
-        <v>01/09/2026</v>
+        <v>12/12/2026</v>
       </c>
       <c r="C67" t="str">
-        <v>25/09/2026</v>
+        <v>20/12/2026</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>C3</v>
+      </c>
+      <c r="B68" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="C68" t="str">
+        <v>04/09/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K68"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/LIRAa Dados.xlsx
+++ b/docs/LIRAa Dados.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:E67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,15 +426,6 @@
       <c r="E1" t="str">
         <v>Alb</v>
       </c>
-      <c r="F1" t="str">
-        <v>Inf.Predial</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Breteau</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Alb</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -452,15 +443,6 @@
       <c r="E2" t="str">
         <v/>
       </c>
-      <c r="F2">
-        <v>4.1</v>
-      </c>
-      <c r="G2">
-        <v>4.1</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -478,15 +460,6 @@
       <c r="E3" t="str">
         <v/>
       </c>
-      <c r="F3">
-        <v>6.3</v>
-      </c>
-      <c r="G3">
-        <v>6.3</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -504,15 +477,6 @@
       <c r="E4" t="str">
         <v/>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3.3</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -530,15 +494,6 @@
       <c r="E5" t="str">
         <v/>
       </c>
-      <c r="F5">
-        <v>0.8</v>
-      </c>
-      <c r="G5">
-        <v>0.8</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -556,15 +511,6 @@
       <c r="E6" t="str">
         <v/>
       </c>
-      <c r="F6">
-        <v>4.8</v>
-      </c>
-      <c r="G6">
-        <v>5.4</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -582,15 +528,6 @@
       <c r="E7" t="str">
         <v/>
       </c>
-      <c r="F7">
-        <v>2.6</v>
-      </c>
-      <c r="G7">
-        <v>2.6</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -608,15 +545,6 @@
       <c r="E8" t="str">
         <v/>
       </c>
-      <c r="F8">
-        <v>3.4</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -634,15 +562,6 @@
       <c r="E9" t="str">
         <v/>
       </c>
-      <c r="F9">
-        <v>1.5</v>
-      </c>
-      <c r="G9">
-        <v>1.5</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -660,15 +579,6 @@
       <c r="E10" t="str">
         <v/>
       </c>
-      <c r="F10">
-        <v>2.6</v>
-      </c>
-      <c r="G10">
-        <v>2.6</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -686,15 +596,6 @@
       <c r="E11" t="str">
         <v/>
       </c>
-      <c r="F11">
-        <v>4.8</v>
-      </c>
-      <c r="G11">
-        <v>5.4</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -712,15 +613,6 @@
       <c r="E12" t="str">
         <v/>
       </c>
-      <c r="F12">
-        <v>6.3</v>
-      </c>
-      <c r="G12">
-        <v>6.3</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -738,15 +630,6 @@
       <c r="E13" t="str">
         <v/>
       </c>
-      <c r="F13">
-        <v>6.7</v>
-      </c>
-      <c r="G13">
-        <v>8</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -764,15 +647,6 @@
       <c r="E14" t="str">
         <v/>
       </c>
-      <c r="F14">
-        <v>2.6</v>
-      </c>
-      <c r="G14">
-        <v>2.6</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -790,15 +664,6 @@
       <c r="E15" t="str">
         <v/>
       </c>
-      <c r="F15">
-        <v>4.8</v>
-      </c>
-      <c r="G15">
-        <v>5.4</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -816,15 +681,6 @@
       <c r="E16" t="str">
         <v/>
       </c>
-      <c r="F16">
-        <v>3.1</v>
-      </c>
-      <c r="G16">
-        <v>3.1</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -842,15 +698,6 @@
       <c r="E17" t="str">
         <v/>
       </c>
-      <c r="F17">
-        <v>2.6</v>
-      </c>
-      <c r="G17">
-        <v>2.6</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -868,15 +715,6 @@
       <c r="E18" t="str">
         <v/>
       </c>
-      <c r="F18">
-        <v>7.6</v>
-      </c>
-      <c r="G18">
-        <v>7.8</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -894,15 +732,6 @@
       <c r="E19" t="str">
         <v/>
       </c>
-      <c r="F19">
-        <v>6.6</v>
-      </c>
-      <c r="G19">
-        <v>6.6</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -920,15 +749,6 @@
       <c r="E20" t="str">
         <v/>
       </c>
-      <c r="F20">
-        <v>2.6</v>
-      </c>
-      <c r="G20">
-        <v>2.6</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -946,15 +766,6 @@
       <c r="E21" t="str">
         <v/>
       </c>
-      <c r="F21">
-        <v>1.6</v>
-      </c>
-      <c r="G21">
-        <v>1.6</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -972,15 +783,6 @@
       <c r="E22" t="str">
         <v/>
       </c>
-      <c r="F22">
-        <v>5.4</v>
-      </c>
-      <c r="G22">
-        <v>5.4</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -998,15 +800,6 @@
       <c r="E23" t="str">
         <v/>
       </c>
-      <c r="F23">
-        <v>2.6</v>
-      </c>
-      <c r="G23">
-        <v>2.6</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1024,15 +817,6 @@
       <c r="E24" t="str">
         <v/>
       </c>
-      <c r="F24">
-        <v>5.4</v>
-      </c>
-      <c r="G24">
-        <v>5.4</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1050,15 +834,6 @@
       <c r="E25" t="str">
         <v/>
       </c>
-      <c r="F25">
-        <v>6.6</v>
-      </c>
-      <c r="G25">
-        <v>6.6</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1076,15 +851,6 @@
       <c r="E26" t="str">
         <v/>
       </c>
-      <c r="F26">
-        <v>3.1</v>
-      </c>
-      <c r="G26">
-        <v>3.1</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1102,15 +868,6 @@
       <c r="E27" t="str">
         <v/>
       </c>
-      <c r="F27">
-        <v>1.5</v>
-      </c>
-      <c r="G27">
-        <v>1.5</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1128,15 +885,6 @@
       <c r="E28" t="str">
         <v/>
       </c>
-      <c r="F28">
-        <v>0.8</v>
-      </c>
-      <c r="G28">
-        <v>0.8</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1154,15 +902,6 @@
       <c r="E29" t="str">
         <v/>
       </c>
-      <c r="F29">
-        <v>1.2</v>
-      </c>
-      <c r="G29">
-        <v>1.2</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1180,15 +919,6 @@
       <c r="E30" t="str">
         <v/>
       </c>
-      <c r="F30">
-        <v>3.4</v>
-      </c>
-      <c r="G30">
-        <v>4</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1206,15 +936,6 @@
       <c r="E31" t="str">
         <v/>
       </c>
-      <c r="F31">
-        <v>1.5</v>
-      </c>
-      <c r="G31">
-        <v>1.5</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1232,15 +953,6 @@
       <c r="E32" t="str">
         <v/>
       </c>
-      <c r="F32">
-        <v>3.7</v>
-      </c>
-      <c r="G32">
-        <v>3.7</v>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1258,15 +970,6 @@
       <c r="E33" t="str">
         <v/>
       </c>
-      <c r="F33">
-        <v>0.8</v>
-      </c>
-      <c r="G33">
-        <v>0.8</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1284,15 +987,6 @@
       <c r="E34" t="str">
         <v/>
       </c>
-      <c r="F34">
-        <v>6</v>
-      </c>
-      <c r="G34">
-        <v>6.2</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1310,15 +1004,6 @@
       <c r="E35" t="str">
         <v/>
       </c>
-      <c r="F35">
-        <v>1.2</v>
-      </c>
-      <c r="G35">
-        <v>1.2</v>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1336,15 +1021,6 @@
       <c r="E36" t="str">
         <v/>
       </c>
-      <c r="F36">
-        <v>1.2</v>
-      </c>
-      <c r="G36">
-        <v>1.2</v>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1362,15 +1038,6 @@
       <c r="E37" t="str">
         <v/>
       </c>
-      <c r="F37">
-        <v>2.6</v>
-      </c>
-      <c r="G37">
-        <v>2.6</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1388,15 +1055,6 @@
       <c r="E38" t="str">
         <v/>
       </c>
-      <c r="F38">
-        <v>1.5</v>
-      </c>
-      <c r="G38">
-        <v>1.5</v>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1414,15 +1072,6 @@
       <c r="E39" t="str">
         <v/>
       </c>
-      <c r="F39">
-        <v>1.5</v>
-      </c>
-      <c r="G39">
-        <v>1.5</v>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1440,15 +1089,6 @@
       <c r="E40" t="str">
         <v/>
       </c>
-      <c r="F40">
-        <v>3.4</v>
-      </c>
-      <c r="G40">
-        <v>4</v>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1466,15 +1106,6 @@
       <c r="E41" t="str">
         <v/>
       </c>
-      <c r="F41">
-        <v>0.8</v>
-      </c>
-      <c r="G41">
-        <v>0.8</v>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1492,15 +1123,6 @@
       <c r="E42" t="str">
         <v/>
       </c>
-      <c r="F42">
-        <v>6.7</v>
-      </c>
-      <c r="G42">
-        <v>8</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1518,15 +1140,6 @@
       <c r="E43" t="str">
         <v/>
       </c>
-      <c r="F43">
-        <v>4.8</v>
-      </c>
-      <c r="G43">
-        <v>5.4</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1544,15 +1157,6 @@
       <c r="E44" t="str">
         <v/>
       </c>
-      <c r="F44">
-        <v>6.3</v>
-      </c>
-      <c r="G44">
-        <v>6.3</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1570,15 +1174,6 @@
       <c r="E45" t="str">
         <v/>
       </c>
-      <c r="F45">
-        <v>4.1</v>
-      </c>
-      <c r="G45">
-        <v>4.1</v>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1596,15 +1191,6 @@
       <c r="E46" t="str">
         <v/>
       </c>
-      <c r="F46">
-        <v>3.1</v>
-      </c>
-      <c r="G46">
-        <v>3.1</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1622,15 +1208,6 @@
       <c r="E47" t="str">
         <v/>
       </c>
-      <c r="F47">
-        <v>7.6</v>
-      </c>
-      <c r="G47">
-        <v>7.8</v>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1648,15 +1225,6 @@
       <c r="E48" t="str">
         <v/>
       </c>
-      <c r="F48">
-        <v>1.2</v>
-      </c>
-      <c r="G48">
-        <v>1.2</v>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1674,15 +1242,6 @@
       <c r="E49" t="str">
         <v/>
       </c>
-      <c r="F49">
-        <v>5.4</v>
-      </c>
-      <c r="G49">
-        <v>5.4</v>
-      </c>
-      <c r="H49" t="str">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1700,15 +1259,6 @@
       <c r="E50" t="str">
         <v/>
       </c>
-      <c r="F50">
-        <v>4.1</v>
-      </c>
-      <c r="G50">
-        <v>4.1</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1726,15 +1276,6 @@
       <c r="E51" t="str">
         <v/>
       </c>
-      <c r="F51">
-        <v>7.6</v>
-      </c>
-      <c r="G51">
-        <v>7.8</v>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1752,15 +1293,6 @@
       <c r="E52" t="str">
         <v/>
       </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52">
-        <v>3.3</v>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1778,15 +1310,6 @@
       <c r="E53" t="str">
         <v/>
       </c>
-      <c r="F53">
-        <v>1.5</v>
-      </c>
-      <c r="G53">
-        <v>1.5</v>
-      </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1804,15 +1327,6 @@
       <c r="E54" t="str">
         <v/>
       </c>
-      <c r="F54">
-        <v>3.4</v>
-      </c>
-      <c r="G54">
-        <v>3.4</v>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1830,15 +1344,6 @@
       <c r="E55" t="str">
         <v/>
       </c>
-      <c r="F55">
-        <v>3.4</v>
-      </c>
-      <c r="G55">
-        <v>4</v>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1856,15 +1361,6 @@
       <c r="E56" t="str">
         <v/>
       </c>
-      <c r="F56">
-        <v>3.7</v>
-      </c>
-      <c r="G56">
-        <v>3.7</v>
-      </c>
-      <c r="H56" t="str">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1882,15 +1378,6 @@
       <c r="E57" t="str">
         <v/>
       </c>
-      <c r="F57">
-        <v>5.5</v>
-      </c>
-      <c r="G57">
-        <v>5.5</v>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1908,15 +1395,6 @@
       <c r="E58" t="str">
         <v/>
       </c>
-      <c r="F58">
-        <v>5.4</v>
-      </c>
-      <c r="G58">
-        <v>5.4</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1934,15 +1412,6 @@
       <c r="E59" t="str">
         <v/>
       </c>
-      <c r="F59">
-        <v>3</v>
-      </c>
-      <c r="G59">
-        <v>3.3</v>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1960,15 +1429,6 @@
       <c r="E60" t="str">
         <v/>
       </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="G60">
-        <v>2.2</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1986,15 +1446,6 @@
       <c r="E61" t="str">
         <v/>
       </c>
-      <c r="F61">
-        <v>4.8</v>
-      </c>
-      <c r="G61">
-        <v>5.4</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2012,15 +1463,6 @@
       <c r="E62" t="str">
         <v/>
       </c>
-      <c r="F62">
-        <v>3.4</v>
-      </c>
-      <c r="G62">
-        <v>4</v>
-      </c>
-      <c r="H62" t="str">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2038,15 +1480,6 @@
       <c r="E63" t="str">
         <v/>
       </c>
-      <c r="F63">
-        <v>6.7</v>
-      </c>
-      <c r="G63">
-        <v>8</v>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -2064,15 +1497,6 @@
       <c r="E64" t="str">
         <v/>
       </c>
-      <c r="F64">
-        <v>3</v>
-      </c>
-      <c r="G64">
-        <v>3.3</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2090,15 +1514,6 @@
       <c r="E65" t="str">
         <v/>
       </c>
-      <c r="F65" t="str">
-        <v>3.7</v>
-      </c>
-      <c r="G65" t="str">
-        <v>3.9</v>
-      </c>
-      <c r="H65" t="str">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2113,26 +1528,15 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>C2</v>
+        <v>INFO_UPD</v>
       </c>
       <c r="B67" t="str">
-        <v>20/09/2026</v>
-      </c>
-      <c r="C67" t="str">
-        <v>24/09/2026</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>INFO_UPD</v>
-      </c>
-      <c r="B68" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E67"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4034,7 +3438,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B57" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -6429,7 +5833,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -9352,7 +8756,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B70" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -11679,7 +11083,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B69" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -14602,7 +14006,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B70" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -16929,7 +16333,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B69" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -19918,7 +19322,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B61" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -22313,7 +21717,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -24708,7 +24112,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>
@@ -26615,7 +26019,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B57" t="str">
-        <v>09/10/2026, 09:12:42</v>
+        <v>09/10/2026, 09:51:05</v>
       </c>
     </row>
   </sheetData>

--- a/docs/LIRAa Dados.xlsx
+++ b/docs/LIRAa Dados.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:H68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,6 +426,15 @@
       <c r="E1" t="str">
         <v>Alb</v>
       </c>
+      <c r="F1" t="str">
+        <v>Inf.Predial</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Breteau</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Alb</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -443,6 +452,15 @@
       <c r="E2" t="str">
         <v/>
       </c>
+      <c r="F2">
+        <v>4.1</v>
+      </c>
+      <c r="G2">
+        <v>4.1</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -460,6 +478,15 @@
       <c r="E3" t="str">
         <v/>
       </c>
+      <c r="F3">
+        <v>6.3</v>
+      </c>
+      <c r="G3">
+        <v>6.3</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -477,6 +504,15 @@
       <c r="E4" t="str">
         <v/>
       </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3.3</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -494,6 +530,15 @@
       <c r="E5" t="str">
         <v/>
       </c>
+      <c r="F5">
+        <v>0.8</v>
+      </c>
+      <c r="G5">
+        <v>0.8</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -511,6 +556,15 @@
       <c r="E6" t="str">
         <v/>
       </c>
+      <c r="F6">
+        <v>4.8</v>
+      </c>
+      <c r="G6">
+        <v>5.4</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -528,6 +582,15 @@
       <c r="E7" t="str">
         <v/>
       </c>
+      <c r="F7">
+        <v>2.6</v>
+      </c>
+      <c r="G7">
+        <v>2.6</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -545,6 +608,15 @@
       <c r="E8" t="str">
         <v/>
       </c>
+      <c r="F8">
+        <v>3.4</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -562,6 +634,15 @@
       <c r="E9" t="str">
         <v/>
       </c>
+      <c r="F9">
+        <v>1.5</v>
+      </c>
+      <c r="G9">
+        <v>1.5</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -579,6 +660,15 @@
       <c r="E10" t="str">
         <v/>
       </c>
+      <c r="F10">
+        <v>2.6</v>
+      </c>
+      <c r="G10">
+        <v>2.6</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -596,6 +686,15 @@
       <c r="E11" t="str">
         <v/>
       </c>
+      <c r="F11">
+        <v>4.8</v>
+      </c>
+      <c r="G11">
+        <v>5.4</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -613,6 +712,15 @@
       <c r="E12" t="str">
         <v/>
       </c>
+      <c r="F12">
+        <v>6.3</v>
+      </c>
+      <c r="G12">
+        <v>6.3</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -630,6 +738,15 @@
       <c r="E13" t="str">
         <v/>
       </c>
+      <c r="F13">
+        <v>6.7</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -647,6 +764,15 @@
       <c r="E14" t="str">
         <v/>
       </c>
+      <c r="F14">
+        <v>2.6</v>
+      </c>
+      <c r="G14">
+        <v>2.6</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -664,6 +790,15 @@
       <c r="E15" t="str">
         <v/>
       </c>
+      <c r="F15">
+        <v>4.8</v>
+      </c>
+      <c r="G15">
+        <v>5.4</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -681,6 +816,15 @@
       <c r="E16" t="str">
         <v/>
       </c>
+      <c r="F16">
+        <v>3.1</v>
+      </c>
+      <c r="G16">
+        <v>3.1</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -698,6 +842,15 @@
       <c r="E17" t="str">
         <v/>
       </c>
+      <c r="F17">
+        <v>2.6</v>
+      </c>
+      <c r="G17">
+        <v>2.6</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -715,6 +868,15 @@
       <c r="E18" t="str">
         <v/>
       </c>
+      <c r="F18">
+        <v>7.6</v>
+      </c>
+      <c r="G18">
+        <v>7.8</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -732,6 +894,15 @@
       <c r="E19" t="str">
         <v/>
       </c>
+      <c r="F19">
+        <v>6.6</v>
+      </c>
+      <c r="G19">
+        <v>6.6</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -749,6 +920,15 @@
       <c r="E20" t="str">
         <v/>
       </c>
+      <c r="F20">
+        <v>2.6</v>
+      </c>
+      <c r="G20">
+        <v>2.6</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -766,6 +946,15 @@
       <c r="E21" t="str">
         <v/>
       </c>
+      <c r="F21">
+        <v>1.6</v>
+      </c>
+      <c r="G21">
+        <v>1.6</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -783,6 +972,15 @@
       <c r="E22" t="str">
         <v/>
       </c>
+      <c r="F22">
+        <v>5.4</v>
+      </c>
+      <c r="G22">
+        <v>5.4</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -800,6 +998,15 @@
       <c r="E23" t="str">
         <v/>
       </c>
+      <c r="F23">
+        <v>2.6</v>
+      </c>
+      <c r="G23">
+        <v>2.6</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -817,6 +1024,15 @@
       <c r="E24" t="str">
         <v/>
       </c>
+      <c r="F24">
+        <v>5.4</v>
+      </c>
+      <c r="G24">
+        <v>5.4</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -834,6 +1050,15 @@
       <c r="E25" t="str">
         <v/>
       </c>
+      <c r="F25">
+        <v>6.6</v>
+      </c>
+      <c r="G25">
+        <v>6.6</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -851,6 +1076,15 @@
       <c r="E26" t="str">
         <v/>
       </c>
+      <c r="F26">
+        <v>3.1</v>
+      </c>
+      <c r="G26">
+        <v>3.1</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -868,6 +1102,15 @@
       <c r="E27" t="str">
         <v/>
       </c>
+      <c r="F27">
+        <v>1.5</v>
+      </c>
+      <c r="G27">
+        <v>1.5</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -885,6 +1128,15 @@
       <c r="E28" t="str">
         <v/>
       </c>
+      <c r="F28">
+        <v>0.8</v>
+      </c>
+      <c r="G28">
+        <v>0.8</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -902,6 +1154,15 @@
       <c r="E29" t="str">
         <v/>
       </c>
+      <c r="F29">
+        <v>1.2</v>
+      </c>
+      <c r="G29">
+        <v>1.2</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -919,6 +1180,15 @@
       <c r="E30" t="str">
         <v/>
       </c>
+      <c r="F30">
+        <v>3.4</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -936,6 +1206,15 @@
       <c r="E31" t="str">
         <v/>
       </c>
+      <c r="F31">
+        <v>1.5</v>
+      </c>
+      <c r="G31">
+        <v>1.5</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -953,6 +1232,15 @@
       <c r="E32" t="str">
         <v/>
       </c>
+      <c r="F32">
+        <v>3.7</v>
+      </c>
+      <c r="G32">
+        <v>3.7</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -970,6 +1258,15 @@
       <c r="E33" t="str">
         <v/>
       </c>
+      <c r="F33">
+        <v>0.8</v>
+      </c>
+      <c r="G33">
+        <v>0.8</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -987,6 +1284,15 @@
       <c r="E34" t="str">
         <v/>
       </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>6.2</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1004,6 +1310,15 @@
       <c r="E35" t="str">
         <v/>
       </c>
+      <c r="F35">
+        <v>1.2</v>
+      </c>
+      <c r="G35">
+        <v>1.2</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1021,6 +1336,15 @@
       <c r="E36" t="str">
         <v/>
       </c>
+      <c r="F36">
+        <v>1.2</v>
+      </c>
+      <c r="G36">
+        <v>1.2</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1038,6 +1362,15 @@
       <c r="E37" t="str">
         <v/>
       </c>
+      <c r="F37">
+        <v>2.6</v>
+      </c>
+      <c r="G37">
+        <v>2.6</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1055,6 +1388,15 @@
       <c r="E38" t="str">
         <v/>
       </c>
+      <c r="F38">
+        <v>1.5</v>
+      </c>
+      <c r="G38">
+        <v>1.5</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1072,6 +1414,15 @@
       <c r="E39" t="str">
         <v/>
       </c>
+      <c r="F39">
+        <v>1.5</v>
+      </c>
+      <c r="G39">
+        <v>1.5</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1089,6 +1440,15 @@
       <c r="E40" t="str">
         <v/>
       </c>
+      <c r="F40">
+        <v>3.4</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1106,6 +1466,15 @@
       <c r="E41" t="str">
         <v/>
       </c>
+      <c r="F41">
+        <v>0.8</v>
+      </c>
+      <c r="G41">
+        <v>0.8</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1123,6 +1492,15 @@
       <c r="E42" t="str">
         <v/>
       </c>
+      <c r="F42">
+        <v>6.7</v>
+      </c>
+      <c r="G42">
+        <v>8</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1140,6 +1518,15 @@
       <c r="E43" t="str">
         <v/>
       </c>
+      <c r="F43">
+        <v>4.8</v>
+      </c>
+      <c r="G43">
+        <v>5.4</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1157,6 +1544,15 @@
       <c r="E44" t="str">
         <v/>
       </c>
+      <c r="F44">
+        <v>6.3</v>
+      </c>
+      <c r="G44">
+        <v>6.3</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1174,6 +1570,15 @@
       <c r="E45" t="str">
         <v/>
       </c>
+      <c r="F45">
+        <v>4.1</v>
+      </c>
+      <c r="G45">
+        <v>4.1</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1191,6 +1596,15 @@
       <c r="E46" t="str">
         <v/>
       </c>
+      <c r="F46">
+        <v>3.1</v>
+      </c>
+      <c r="G46">
+        <v>3.1</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1208,6 +1622,15 @@
       <c r="E47" t="str">
         <v/>
       </c>
+      <c r="F47">
+        <v>7.6</v>
+      </c>
+      <c r="G47">
+        <v>7.8</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1225,6 +1648,15 @@
       <c r="E48" t="str">
         <v/>
       </c>
+      <c r="F48">
+        <v>1.2</v>
+      </c>
+      <c r="G48">
+        <v>1.2</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1242,6 +1674,15 @@
       <c r="E49" t="str">
         <v/>
       </c>
+      <c r="F49">
+        <v>5.4</v>
+      </c>
+      <c r="G49">
+        <v>5.4</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1259,6 +1700,15 @@
       <c r="E50" t="str">
         <v/>
       </c>
+      <c r="F50">
+        <v>4.1</v>
+      </c>
+      <c r="G50">
+        <v>4.1</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1276,6 +1726,15 @@
       <c r="E51" t="str">
         <v/>
       </c>
+      <c r="F51">
+        <v>7.6</v>
+      </c>
+      <c r="G51">
+        <v>7.8</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1293,6 +1752,15 @@
       <c r="E52" t="str">
         <v/>
       </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>3.3</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1310,6 +1778,15 @@
       <c r="E53" t="str">
         <v/>
       </c>
+      <c r="F53">
+        <v>1.5</v>
+      </c>
+      <c r="G53">
+        <v>1.5</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1327,6 +1804,15 @@
       <c r="E54" t="str">
         <v/>
       </c>
+      <c r="F54">
+        <v>3.4</v>
+      </c>
+      <c r="G54">
+        <v>3.4</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1344,6 +1830,15 @@
       <c r="E55" t="str">
         <v/>
       </c>
+      <c r="F55">
+        <v>3.4</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1361,6 +1856,15 @@
       <c r="E56" t="str">
         <v/>
       </c>
+      <c r="F56">
+        <v>3.7</v>
+      </c>
+      <c r="G56">
+        <v>3.7</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1378,6 +1882,15 @@
       <c r="E57" t="str">
         <v/>
       </c>
+      <c r="F57">
+        <v>5.5</v>
+      </c>
+      <c r="G57">
+        <v>5.5</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1395,6 +1908,15 @@
       <c r="E58" t="str">
         <v/>
       </c>
+      <c r="F58">
+        <v>5.4</v>
+      </c>
+      <c r="G58">
+        <v>5.4</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1412,6 +1934,15 @@
       <c r="E59" t="str">
         <v/>
       </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>3.3</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1429,6 +1960,15 @@
       <c r="E60" t="str">
         <v/>
       </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>2.2</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1446,6 +1986,15 @@
       <c r="E61" t="str">
         <v/>
       </c>
+      <c r="F61">
+        <v>4.8</v>
+      </c>
+      <c r="G61">
+        <v>5.4</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1463,6 +2012,15 @@
       <c r="E62" t="str">
         <v/>
       </c>
+      <c r="F62">
+        <v>3.4</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1480,6 +2038,15 @@
       <c r="E63" t="str">
         <v/>
       </c>
+      <c r="F63">
+        <v>6.7</v>
+      </c>
+      <c r="G63">
+        <v>8</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1497,6 +2064,15 @@
       <c r="E64" t="str">
         <v/>
       </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>3.3</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -1514,6 +2090,15 @@
       <c r="E65" t="str">
         <v/>
       </c>
+      <c r="F65" t="str">
+        <v>3.7</v>
+      </c>
+      <c r="G65" t="str">
+        <v>3.9</v>
+      </c>
+      <c r="H65" t="str">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -1528,15 +2113,26 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
+        <v>C2</v>
+      </c>
+      <c r="B67" t="str">
+        <v>20/09/2026</v>
+      </c>
+      <c r="C67" t="str">
+        <v>24/09/2026</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
         <v>INFO_UPD</v>
       </c>
-      <c r="B67" t="str">
-        <v>09/10/2026, 09:51:05</v>
+      <c r="B68" t="str">
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H68"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3438,7 +4034,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B57" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -5833,7 +6429,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -8756,7 +9352,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B70" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -11083,7 +11679,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B69" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -14006,7 +14602,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B70" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -16333,7 +16929,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B69" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -19322,7 +19918,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B61" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -21717,7 +22313,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -24112,7 +24708,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B58" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
@@ -26019,7 +26615,7 @@
         <v>INFO_UPD</v>
       </c>
       <c r="B57" t="str">
-        <v>09/10/2026, 09:51:05</v>
+        <v>09/10/2026, 09:58:03</v>
       </c>
     </row>
   </sheetData>
